--- a/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
+++ b/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -2702,17 +2694,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -2793,17 +2777,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -2884,17 +2860,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -2975,17 +2943,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -3066,17 +3026,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -3157,17 +3109,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -3248,17 +3192,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -3338,16 +3274,8 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3391,16 +3319,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3444,16 +3364,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3497,16 +3409,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3550,16 +3454,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3603,16 +3499,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3656,16 +3544,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3709,16 +3589,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3762,16 +3634,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3815,16 +3679,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3868,16 +3724,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3921,16 +3769,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2170A01</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2170001</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3974,16 +3814,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4027,16 +3859,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4080,16 +3904,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4133,16 +3949,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4186,16 +3994,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4239,16 +4039,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4292,16 +4084,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4345,16 +4129,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4398,16 +4174,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4451,16 +4219,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2170A02</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2170002</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
+++ b/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2170A04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
+++ b/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>2170004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
+++ b/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3572,22 +3572,22 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3640,22 +3640,22 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3708,22 +3708,22 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3776,22 +3776,22 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3844,22 +3844,22 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3912,22 +3912,22 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3980,22 +3980,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4048,22 +4048,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4116,22 +4116,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2170A04</t>
+          <t>2170A05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2170004</t>
+          <t>2170005</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 H보장보험Ⅰ 무배당 일반가입형(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4244,686 +4244,6 @@
         <v>30</v>
       </c>
       <c r="O26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>90</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>90</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>10</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>90</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>15</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>90</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>20</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N30</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>90</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>30</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>100</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>100</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>10</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>100</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>15</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>100</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>20</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2170A04</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2170004</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 H보장보험Ⅰ 무배당 간편가입형(2년)(해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N30</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>100</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>30</v>
-      </c>
-      <c r="O36" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
+++ b/output/upload/S00027_2170_H보장보험Ⅰ_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
